--- a/Codes/Arduino_Codes/PinOut_ESP32_Mantis.xlsx
+++ b/Codes/Arduino_Codes/PinOut_ESP32_Mantis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shernandsanc\Desktop\ColmillosRoboticsITAM\Limpiador_de_Playa\Codes\Arduino_Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2D841C-538E-41EC-AF88-BADA2C143AD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1373A96-A118-4629-9EE2-6CD7DDBF3658}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="15600" windowHeight="11160" activeTab="1" xr2:uid="{C7E1983F-B78C-4A84-9751-666A9F6E4C32}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>PinOut</t>
   </si>
@@ -280,16 +280,46 @@
     <t>RMot_pwm</t>
   </si>
   <si>
-    <t>Cytron_PWM1</t>
-  </si>
-  <si>
-    <t>Cytron_PWM2</t>
-  </si>
-  <si>
-    <t>Cytron_DIR2</t>
-  </si>
-  <si>
-    <t>Cytron_DIR1</t>
+    <t>Sweeper_dir</t>
+  </si>
+  <si>
+    <t>Sweeper_pwm</t>
+  </si>
+  <si>
+    <t>Cytron1Ch_DIR</t>
+  </si>
+  <si>
+    <t>Cytron1Ch_PWM</t>
+  </si>
+  <si>
+    <t>Cytron2Ch_DIR1</t>
+  </si>
+  <si>
+    <t>Cytron2Ch_PWM1</t>
+  </si>
+  <si>
+    <t>Cytron2Ch_DIR2</t>
+  </si>
+  <si>
+    <t>Cytron2Ch_PWM2</t>
+  </si>
+  <si>
+    <t>IMU_SCL</t>
+  </si>
+  <si>
+    <t>IMU_SDA</t>
+  </si>
+  <si>
+    <t>LContainer</t>
+  </si>
+  <si>
+    <t>RContainer</t>
+  </si>
+  <si>
+    <t>LServo@5V</t>
+  </si>
+  <si>
+    <t>RServo@5V</t>
   </si>
 </sst>
 </file>
@@ -500,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -568,6 +598,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1535,8 +1568,8 @@
     <col min="5" max="5" width="9.5703125" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1601,8 +1634,12 @@
       <c r="I4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="J4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="L4" s="17"/>
       <c r="M4" s="20"/>
     </row>
@@ -1619,7 +1656,7 @@
       <c r="I5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="17"/>
+      <c r="J5" s="20"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="20"/>
@@ -1637,7 +1674,7 @@
       <c r="I6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="17"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="20"/>
@@ -1655,8 +1692,12 @@
       <c r="I7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
+      <c r="J7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="L7" s="17"/>
       <c r="M7" s="20"/>
     </row>
@@ -1671,8 +1712,12 @@
       <c r="I8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
+      <c r="J8" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>96</v>
+      </c>
       <c r="L8" s="17"/>
       <c r="M8" s="20"/>
     </row>
@@ -1687,8 +1732,12 @@
       <c r="I9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="J9" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>97</v>
+      </c>
       <c r="L9" s="17"/>
       <c r="M9" s="20"/>
     </row>
@@ -1703,8 +1752,12 @@
       <c r="I10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
+      <c r="J10" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>86</v>
+      </c>
       <c r="L10" s="17"/>
       <c r="M10" s="20"/>
     </row>
@@ -1719,8 +1772,12 @@
       <c r="I11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
+      <c r="J11" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>87</v>
+      </c>
       <c r="L11" s="17"/>
       <c r="M11" s="20"/>
     </row>
@@ -1739,7 +1796,7 @@
         <v>81</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L12" s="17"/>
       <c r="M12" s="20"/>
@@ -1759,7 +1816,7 @@
         <v>82</v>
       </c>
       <c r="K13" s="29" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L13" s="17"/>
       <c r="M13" s="20"/>
@@ -1779,7 +1836,7 @@
         <v>81</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L14" s="17"/>
       <c r="M14" s="20"/>
@@ -1799,7 +1856,7 @@
         <v>83</v>
       </c>
       <c r="K15" s="29" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L15" s="17"/>
       <c r="M15" s="20"/>
